--- a/25_Lamya_Harsh_DS/apr10.xlsx
+++ b/25_Lamya_Harsh_DS/apr10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_Lamya_Harsh_DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90B2A03-1CFA-4E53-8D40-2DB49268F523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E215E009-BE9A-42A8-BE29-86E7AA7B702A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{9553A1CE-9236-4A8D-B110-BC83E5BA013D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9553A1CE-9236-4A8D-B110-BC83E5BA013D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="52">
   <si>
     <t>Qty:</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>Per Capita Income</t>
+  </si>
+  <si>
+    <t>Transpose</t>
   </si>
 </sst>
 </file>
@@ -364,9 +367,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -384,6 +384,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,7 +804,7 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="18">
         <v>45392</v>
       </c>
       <c r="E5" s="1"/>
@@ -866,9 +869,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9AECFB-8736-4594-A13F-D7F2A47657F0}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -876,7 +880,7 @@
     <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -896,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>79</v>
       </c>
@@ -916,7 +920,7 @@
         <v>75.53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>261</v>
       </c>
@@ -936,7 +940,7 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2766</v>
       </c>
@@ -956,7 +960,7 @@
         <v>61.05</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>281</v>
       </c>
@@ -976,7 +980,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2744</v>
       </c>
@@ -996,7 +1000,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2742</v>
       </c>
@@ -1016,9 +1020,152 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>79</v>
+      </c>
+      <c r="C13">
+        <v>261</v>
+      </c>
+      <c r="D13">
+        <v>2766</v>
+      </c>
+      <c r="E13">
+        <v>281</v>
+      </c>
+      <c r="F13">
+        <v>2744</v>
+      </c>
+      <c r="G13">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>86</v>
+      </c>
+      <c r="C15">
+        <v>80</v>
+      </c>
+      <c r="D15">
+        <v>13</v>
+      </c>
+      <c r="E15">
+        <v>46</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>68.7</v>
+      </c>
+      <c r="C16">
+        <v>60.5</v>
+      </c>
+      <c r="D16">
+        <v>72.3</v>
+      </c>
+      <c r="E16">
+        <v>52.2</v>
+      </c>
+      <c r="F16">
+        <v>68.8</v>
+      </c>
+      <c r="G16">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <v>65.7</v>
+      </c>
+      <c r="C17">
+        <v>60</v>
+      </c>
+      <c r="D17">
+        <v>82.9</v>
+      </c>
+      <c r="E17">
+        <v>52.5</v>
+      </c>
+      <c r="F17">
+        <v>72.8</v>
+      </c>
+      <c r="G17">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>75.53</v>
+      </c>
+      <c r="C18">
+        <v>62.2</v>
+      </c>
+      <c r="D18">
+        <v>61.05</v>
+      </c>
+      <c r="E18">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="F18">
+        <v>40</v>
+      </c>
+      <c r="G18">
+        <v>38.799999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1028,12 +1175,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626018C6-79CB-4C67-97B0-BA52263C73CB}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
@@ -1108,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" s="3"/>
     </row>
@@ -1181,14 +1329,14 @@
       <c r="K9" s="3"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="19"/>
+      <c r="D11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1211,12 +1359,20 @@
       <c r="A14" t="s">
         <v>24</v>
       </c>
+      <c r="B14">
+        <f>MATCH(B13, A2:A7, 0)</f>
+        <v>2</v>
+      </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
+      <c r="E14" t="str">
+        <f>INDEX(A1:A7, E13)</f>
+        <v>Rajkot</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1238,84 +1394,98 @@
       <c r="A17" t="s">
         <v>28</v>
       </c>
+      <c r="B17">
+        <f>MATCH(B16, B1:F1, 0)</f>
+        <v>2</v>
+      </c>
       <c r="D17" t="s">
         <v>29</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
         <v>30</v>
       </c>
+      <c r="E18">
+        <f>INDEX(A1:C7, E16, E17)</f>
+        <v>64.900000000000006</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="B19" t="e">
+        <f>MATCH(B4, A1:C7, 0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="F22" t="s">
+      <c r="C23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="F23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="F23" s="9" t="s">
+      <c r="C24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="F24" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="7"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="9"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1326,10 +1496,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{5A948273-59B8-4B6B-A748-8EEBEC82718E}">
       <formula1>$B$1:$E$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 J4 B13" xr:uid="{F7871551-7630-48E0-B051-1F83D0FD01BB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23 J4 B13" xr:uid="{F7871551-7630-48E0-B051-1F83D0FD01BB}">
       <formula1>$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23" xr:uid="{F1EE1BF4-AA00-4812-97D4-86CDDCA1D907}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C24" xr:uid="{F1EE1BF4-AA00-4812-97D4-86CDDCA1D907}">
       <formula1>$A$1:$D$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -1350,124 +1520,130 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>41</v>
+      <c r="H3" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <v>200</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>97</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>98</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2">
+        <f>HLOOKUP(H3, C3:E6, 4, FALSE)</f>
+        <v>32</v>
+      </c>
     </row>
     <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>20</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>22</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>21</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2">
+        <f>HLOOKUP(H3, Table_57[[#All],[SR Tendulkar]:[V Kohli]], 3, FALSE)</f>
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <v>32</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>35</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>100</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>25</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>125</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>20</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="16"/>
+      <c r="C13" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/25_Lamya_Harsh_DS/apr10.xlsx
+++ b/25_Lamya_Harsh_DS/apr10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_Lamya_Harsh_DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E215E009-BE9A-42A8-BE29-86E7AA7B702A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022A8E35-715F-4077-97C7-4688F0AE0681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9553A1CE-9236-4A8D-B110-BC83E5BA013D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{9553A1CE-9236-4A8D-B110-BC83E5BA013D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="2" r:id="rId1"/>
@@ -1390,7 +1390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
         <v>30</v>
       </c>
@@ -1414,37 +1414,41 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B19" t="e">
-        <f>MATCH(B4, A1:C7, 0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B19" t="str">
+        <f>IFERROR(MATCH(B4, A1:C7, 0), "Wrong data selected.")</f>
+        <v>Wrong data selected.</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" s="5"/>
       <c r="F23" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <f>MATCH(C23, A1:A7, 0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>26</v>
@@ -1456,8 +1460,12 @@
       <c r="F24" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <f>MATCH(C24, A1:F1, 0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>35</v>
@@ -1465,23 +1473,29 @@
       <c r="C25" s="7"/>
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="9"/>
+      <c r="C26" s="9">
+        <f>INDEX(A1:F7, G23, G24)</f>
+        <v>2400</v>
+      </c>
       <c r="D26" s="5"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="9">
+        <f>INDEX(A1:F7, MATCH(C23, A1:A7, 0), MATCH(C24, A1:F1,0))</f>
+        <v>2400</v>
+      </c>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
